--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123977</v>
+        <v>125123981</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730115</v>
+        <v>729951</v>
       </c>
       <c r="R3" t="n">
-        <v>7086341</v>
+        <v>7086320</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123979</v>
+        <v>125123975</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729941</v>
+        <v>730182</v>
       </c>
       <c r="R4" t="n">
-        <v>7086397</v>
+        <v>7086404</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123983</v>
+        <v>125123982</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729955</v>
+        <v>729957</v>
       </c>
       <c r="R5" t="n">
-        <v>7086325</v>
+        <v>7086326</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123976</v>
+        <v>125123983</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730120</v>
+        <v>729955</v>
       </c>
       <c r="R6" t="n">
-        <v>7086328</v>
+        <v>7086325</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123981</v>
+        <v>125123976</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729951</v>
+        <v>730120</v>
       </c>
       <c r="R8" t="n">
-        <v>7086320</v>
+        <v>7086328</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125123975</v>
+        <v>125123979</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730182</v>
+        <v>729941</v>
       </c>
       <c r="R9" t="n">
-        <v>7086404</v>
+        <v>7086397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123982</v>
+        <v>125123977</v>
       </c>
       <c r="B10" t="n">
         <v>90977</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729957</v>
+        <v>730115</v>
       </c>
       <c r="R10" t="n">
-        <v>7086326</v>
+        <v>7086341</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123980</v>
+        <v>125123982</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729953</v>
+        <v>729957</v>
       </c>
       <c r="R2" t="n">
-        <v>7086371</v>
+        <v>7086326</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123981</v>
+        <v>125123976</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729951</v>
+        <v>730120</v>
       </c>
       <c r="R3" t="n">
-        <v>7086320</v>
+        <v>7086328</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123975</v>
+        <v>125123979</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730182</v>
+        <v>729941</v>
       </c>
       <c r="R4" t="n">
-        <v>7086404</v>
+        <v>7086397</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123982</v>
+        <v>125123977</v>
       </c>
       <c r="B5" t="n">
         <v>90977</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729957</v>
+        <v>730115</v>
       </c>
       <c r="R5" t="n">
-        <v>7086326</v>
+        <v>7086341</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123983</v>
+        <v>125123981</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729955</v>
+        <v>729951</v>
       </c>
       <c r="R6" t="n">
-        <v>7086325</v>
+        <v>7086320</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123978</v>
+        <v>125123980</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729934</v>
+        <v>729953</v>
       </c>
       <c r="R7" t="n">
-        <v>7086401</v>
+        <v>7086371</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123976</v>
+        <v>125123983</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730120</v>
+        <v>729955</v>
       </c>
       <c r="R8" t="n">
-        <v>7086328</v>
+        <v>7086325</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125123979</v>
+        <v>125123975</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729941</v>
+        <v>730182</v>
       </c>
       <c r="R9" t="n">
-        <v>7086397</v>
+        <v>7086404</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123977</v>
+        <v>125123978</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730115</v>
+        <v>729934</v>
       </c>
       <c r="R10" t="n">
-        <v>7086341</v>
+        <v>7086401</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123980</v>
+        <v>125123983</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729953</v>
+        <v>729955</v>
       </c>
       <c r="R7" t="n">
-        <v>7086371</v>
+        <v>7086325</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123983</v>
+        <v>125123980</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729955</v>
+        <v>729953</v>
       </c>
       <c r="R8" t="n">
-        <v>7086325</v>
+        <v>7086371</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123983</v>
+        <v>125123980</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729955</v>
+        <v>729953</v>
       </c>
       <c r="R7" t="n">
-        <v>7086325</v>
+        <v>7086371</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123980</v>
+        <v>125123983</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729953</v>
+        <v>729955</v>
       </c>
       <c r="R8" t="n">
-        <v>7086371</v>
+        <v>7086325</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123982</v>
+        <v>125123977</v>
       </c>
       <c r="B2" t="n">
         <v>90977</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729957</v>
+        <v>730115</v>
       </c>
       <c r="R2" t="n">
-        <v>7086326</v>
+        <v>7086341</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123976</v>
+        <v>125123982</v>
       </c>
       <c r="B3" t="n">
         <v>90977</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730120</v>
+        <v>729957</v>
       </c>
       <c r="R3" t="n">
-        <v>7086328</v>
+        <v>7086326</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123979</v>
+        <v>125123978</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729941</v>
+        <v>729934</v>
       </c>
       <c r="R4" t="n">
-        <v>7086397</v>
+        <v>7086401</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123977</v>
+        <v>125123981</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730115</v>
+        <v>729951</v>
       </c>
       <c r="R5" t="n">
-        <v>7086341</v>
+        <v>7086320</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123981</v>
+        <v>125123983</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729951</v>
+        <v>729955</v>
       </c>
       <c r="R6" t="n">
-        <v>7086320</v>
+        <v>7086325</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123980</v>
+        <v>125123976</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729953</v>
+        <v>730120</v>
       </c>
       <c r="R7" t="n">
-        <v>7086371</v>
+        <v>7086328</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123983</v>
+        <v>125123979</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729955</v>
+        <v>729941</v>
       </c>
       <c r="R8" t="n">
-        <v>7086325</v>
+        <v>7086397</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125123975</v>
+        <v>125123980</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730182</v>
+        <v>729953</v>
       </c>
       <c r="R9" t="n">
-        <v>7086404</v>
+        <v>7086371</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123978</v>
+        <v>125123975</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729934</v>
+        <v>730182</v>
       </c>
       <c r="R10" t="n">
-        <v>7086401</v>
+        <v>7086404</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123977</v>
+        <v>125123978</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730115</v>
+        <v>729934</v>
       </c>
       <c r="R2" t="n">
-        <v>7086341</v>
+        <v>7086401</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123982</v>
+        <v>125123977</v>
       </c>
       <c r="B3" t="n">
         <v>90977</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729957</v>
+        <v>730115</v>
       </c>
       <c r="R3" t="n">
-        <v>7086326</v>
+        <v>7086341</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123978</v>
+        <v>125123975</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729934</v>
+        <v>730182</v>
       </c>
       <c r="R4" t="n">
-        <v>7086401</v>
+        <v>7086404</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123981</v>
+        <v>125123976</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729951</v>
+        <v>730120</v>
       </c>
       <c r="R5" t="n">
-        <v>7086320</v>
+        <v>7086328</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123983</v>
+        <v>125123981</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729955</v>
+        <v>729951</v>
       </c>
       <c r="R6" t="n">
-        <v>7086325</v>
+        <v>7086320</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123976</v>
+        <v>125123980</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730120</v>
+        <v>729953</v>
       </c>
       <c r="R7" t="n">
-        <v>7086328</v>
+        <v>7086371</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123979</v>
+        <v>125123983</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729941</v>
+        <v>729955</v>
       </c>
       <c r="R8" t="n">
-        <v>7086397</v>
+        <v>7086325</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125123980</v>
+        <v>125123979</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729953</v>
+        <v>729941</v>
       </c>
       <c r="R9" t="n">
-        <v>7086371</v>
+        <v>7086397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123975</v>
+        <v>125123982</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730182</v>
+        <v>729957</v>
       </c>
       <c r="R10" t="n">
-        <v>7086404</v>
+        <v>7086326</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123978</v>
+        <v>125123980</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729934</v>
+        <v>729953</v>
       </c>
       <c r="R2" t="n">
-        <v>7086401</v>
+        <v>7086371</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123977</v>
+        <v>125123983</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730115</v>
+        <v>729955</v>
       </c>
       <c r="R3" t="n">
-        <v>7086341</v>
+        <v>7086325</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123975</v>
+        <v>125123976</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730182</v>
+        <v>730120</v>
       </c>
       <c r="R4" t="n">
-        <v>7086404</v>
+        <v>7086328</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123976</v>
+        <v>125123975</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730120</v>
+        <v>730182</v>
       </c>
       <c r="R5" t="n">
-        <v>7086328</v>
+        <v>7086404</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123980</v>
+        <v>125123978</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729953</v>
+        <v>729934</v>
       </c>
       <c r="R7" t="n">
-        <v>7086371</v>
+        <v>7086401</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123983</v>
+        <v>125123982</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729955</v>
+        <v>729957</v>
       </c>
       <c r="R8" t="n">
-        <v>7086325</v>
+        <v>7086326</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123982</v>
+        <v>125123977</v>
       </c>
       <c r="B10" t="n">
         <v>90977</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729957</v>
+        <v>730115</v>
       </c>
       <c r="R10" t="n">
-        <v>7086326</v>
+        <v>7086341</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123980</v>
+        <v>125123983</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729953</v>
+        <v>729955</v>
       </c>
       <c r="R2" t="n">
-        <v>7086371</v>
+        <v>7086325</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123983</v>
+        <v>125123976</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729955</v>
+        <v>730120</v>
       </c>
       <c r="R3" t="n">
-        <v>7086325</v>
+        <v>7086328</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123976</v>
+        <v>125123981</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730120</v>
+        <v>729951</v>
       </c>
       <c r="R4" t="n">
-        <v>7086328</v>
+        <v>7086320</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123975</v>
+        <v>125123979</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730182</v>
+        <v>729941</v>
       </c>
       <c r="R5" t="n">
-        <v>7086404</v>
+        <v>7086397</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123981</v>
+        <v>125123975</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729951</v>
+        <v>730182</v>
       </c>
       <c r="R6" t="n">
-        <v>7086320</v>
+        <v>7086404</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123978</v>
+        <v>125123977</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729934</v>
+        <v>730115</v>
       </c>
       <c r="R7" t="n">
-        <v>7086401</v>
+        <v>7086341</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123982</v>
+        <v>125123978</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729957</v>
+        <v>729934</v>
       </c>
       <c r="R8" t="n">
-        <v>7086326</v>
+        <v>7086401</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125123979</v>
+        <v>125123980</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729941</v>
+        <v>729953</v>
       </c>
       <c r="R9" t="n">
-        <v>7086397</v>
+        <v>7086371</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123977</v>
+        <v>125123982</v>
       </c>
       <c r="B10" t="n">
         <v>90977</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730115</v>
+        <v>729957</v>
       </c>
       <c r="R10" t="n">
-        <v>7086341</v>
+        <v>7086326</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123977</v>
+        <v>125123978</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730115</v>
+        <v>729934</v>
       </c>
       <c r="R7" t="n">
-        <v>7086341</v>
+        <v>7086401</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123978</v>
+        <v>125123977</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729934</v>
+        <v>730115</v>
       </c>
       <c r="R8" t="n">
-        <v>7086401</v>
+        <v>7086341</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123983</v>
+        <v>125123980</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729955</v>
+        <v>729953</v>
       </c>
       <c r="R2" t="n">
-        <v>7086325</v>
+        <v>7086371</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123976</v>
+        <v>125123982</v>
       </c>
       <c r="B3" t="n">
         <v>90977</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730120</v>
+        <v>729957</v>
       </c>
       <c r="R3" t="n">
-        <v>7086328</v>
+        <v>7086326</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123981</v>
+        <v>125123975</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729951</v>
+        <v>730182</v>
       </c>
       <c r="R4" t="n">
-        <v>7086320</v>
+        <v>7086404</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123979</v>
+        <v>125123978</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729941</v>
+        <v>729934</v>
       </c>
       <c r="R5" t="n">
-        <v>7086397</v>
+        <v>7086401</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123975</v>
+        <v>125123979</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730182</v>
+        <v>729941</v>
       </c>
       <c r="R6" t="n">
-        <v>7086404</v>
+        <v>7086397</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123978</v>
+        <v>125123977</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729934</v>
+        <v>730115</v>
       </c>
       <c r="R7" t="n">
-        <v>7086401</v>
+        <v>7086341</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123977</v>
+        <v>125123981</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730115</v>
+        <v>729951</v>
       </c>
       <c r="R8" t="n">
-        <v>7086341</v>
+        <v>7086320</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1368,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125123980</v>
+        <v>125123976</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729953</v>
+        <v>730120</v>
       </c>
       <c r="R9" t="n">
-        <v>7086371</v>
+        <v>7086328</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123982</v>
+        <v>125123983</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729957</v>
+        <v>729955</v>
       </c>
       <c r="R10" t="n">
-        <v>7086326</v>
+        <v>7086325</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123980</v>
+        <v>125123977</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729953</v>
+        <v>730115</v>
       </c>
       <c r="R2" t="n">
-        <v>7086371</v>
+        <v>7086341</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123982</v>
+        <v>125123976</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729957</v>
+        <v>730120</v>
       </c>
       <c r="R3" t="n">
-        <v>7086326</v>
+        <v>7086328</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123975</v>
+        <v>125123981</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730182</v>
+        <v>729951</v>
       </c>
       <c r="R4" t="n">
-        <v>7086404</v>
+        <v>7086320</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123978</v>
+        <v>125123980</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729934</v>
+        <v>729953</v>
       </c>
       <c r="R5" t="n">
-        <v>7086401</v>
+        <v>7086371</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123979</v>
+        <v>125123978</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>91166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729941</v>
+        <v>729934</v>
       </c>
       <c r="R6" t="n">
-        <v>7086397</v>
+        <v>7086401</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123977</v>
+        <v>125123979</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730115</v>
+        <v>729941</v>
       </c>
       <c r="R7" t="n">
-        <v>7086341</v>
+        <v>7086397</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123981</v>
+        <v>125123975</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729951</v>
+        <v>730182</v>
       </c>
       <c r="R8" t="n">
-        <v>7086320</v>
+        <v>7086404</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125123976</v>
+        <v>125123983</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>91166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730120</v>
+        <v>729955</v>
       </c>
       <c r="R9" t="n">
-        <v>7086328</v>
+        <v>7086325</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123983</v>
+        <v>125123982</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729955</v>
+        <v>729957</v>
       </c>
       <c r="R10" t="n">
-        <v>7086325</v>
+        <v>7086326</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123977</v>
+        <v>125123975</v>
       </c>
       <c r="B2" t="n">
-        <v>91131</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730115</v>
+        <v>730182</v>
       </c>
       <c r="R2" t="n">
-        <v>7086341</v>
+        <v>7086404</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123981</v>
+        <v>125123980</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729951</v>
+        <v>729953</v>
       </c>
       <c r="R4" t="n">
-        <v>7086320</v>
+        <v>7086371</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123980</v>
+        <v>125123977</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>91131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729953</v>
+        <v>730115</v>
       </c>
       <c r="R5" t="n">
-        <v>7086371</v>
+        <v>7086341</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123978</v>
+        <v>125123982</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
+        <v>91131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729934</v>
+        <v>729957</v>
       </c>
       <c r="R6" t="n">
-        <v>7086401</v>
+        <v>7086326</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123979</v>
+        <v>125123983</v>
       </c>
       <c r="B7" t="n">
-        <v>91131</v>
+        <v>91166</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729941</v>
+        <v>729955</v>
       </c>
       <c r="R7" t="n">
-        <v>7086397</v>
+        <v>7086325</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123975</v>
+        <v>125123979</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730182</v>
+        <v>729941</v>
       </c>
       <c r="R8" t="n">
-        <v>7086404</v>
+        <v>7086397</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125123983</v>
+        <v>125123978</v>
       </c>
       <c r="B9" t="n">
         <v>91166</v>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729955</v>
+        <v>729934</v>
       </c>
       <c r="R9" t="n">
-        <v>7086325</v>
+        <v>7086401</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123982</v>
+        <v>125123981</v>
       </c>
       <c r="B10" t="n">
-        <v>91131</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729957</v>
+        <v>729951</v>
       </c>
       <c r="R10" t="n">
-        <v>7086326</v>
+        <v>7086320</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1572,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>125123975</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123976</v>
+        <v>125123982</v>
       </c>
       <c r="B3" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730120</v>
+        <v>729957</v>
       </c>
       <c r="R3" t="n">
-        <v>7086328</v>
+        <v>7086326</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123980</v>
+        <v>125123981</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729953</v>
+        <v>729951</v>
       </c>
       <c r="R4" t="n">
-        <v>7086371</v>
+        <v>7086320</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -955,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,37 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123977</v>
+        <v>125123978</v>
       </c>
       <c r="B5" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730115</v>
+        <v>729934</v>
       </c>
       <c r="R5" t="n">
-        <v>7086341</v>
+        <v>7086401</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,37 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123982</v>
+        <v>125123980</v>
       </c>
       <c r="B6" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729957</v>
+        <v>729953</v>
       </c>
       <c r="R6" t="n">
-        <v>7086326</v>
+        <v>7086371</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123983</v>
+        <v>125123976</v>
       </c>
       <c r="B7" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729955</v>
+        <v>730120</v>
       </c>
       <c r="R7" t="n">
-        <v>7086325</v>
+        <v>7086328</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123979</v>
+        <v>125123977</v>
       </c>
       <c r="B8" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729941</v>
+        <v>730115</v>
       </c>
       <c r="R8" t="n">
-        <v>7086397</v>
+        <v>7086341</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,37 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125123978</v>
+        <v>125123979</v>
       </c>
       <c r="B9" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729934</v>
+        <v>729941</v>
       </c>
       <c r="R9" t="n">
-        <v>7086401</v>
+        <v>7086397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,15 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123981</v>
+        <v>125123983</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729951</v>
+        <v>729955</v>
       </c>
       <c r="R10" t="n">
-        <v>7086320</v>
+        <v>7086325</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1569,11 +1529,6 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1595,6 +1550,107 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125773739</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kuxmyberget östra, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>730158</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7086343</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>125773739</v>
       </c>
       <c r="B11" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 21711-2025 artfynd.xlsx
+++ b/artfynd/A 21711-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>125773739</v>
       </c>
       <c r="B11" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
